--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0003.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0003.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Một công trình hoành tráng nằm trên trục trung tâm của Jinzhou. Nó không chỉ đảm nhiệm chức năng tiếp đón quan trọng và thảo luận các vấn đề trọng đại, mà còn là biểu tượng của hy vọng cho người dân Huanglong.</t>
+          <t>Một công trình vĩ đại nằm trên trục trung tâm của Jinzhou. Không chỉ đảm nhiệm chức năng tiếp đón quan trọng và thảo luận các vấn đề trọng đại, nó còn là biểu tượng của hy vọng cho người dân Huanglong.</t>
         </is>
       </c>
     </row>
@@ -776,8 +776,8 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Khả năng Resonance của Cantarella cho phép cô điều khiển chất độc. Nó gây ra những ảo giác sống động cho mục tiêu, có thể là những khát khao sâu thẳm nhất hoặc những ảo ảnh được dày công tạo ra.
-Like mọi khả năng của gia tộc Fisalia, nó phải trả giá. Sử dụng quá lâu có thể khiến người dùng bị mắc kẹt trong chính giấc mơ của mình, làm mờ ranh giới giữa thực tại và ảo giác mãi mãi.</t>
+          <t>Khả năng Cộng Hưởng của Cantarella cho phép cô điều khiển chất độc. Nó gây ra những ảo giác sống động cho mục tiêu, có thể là những khát khao sâu thẳm nhất hoặc những ảo ảnh được dày công tạo ra.
+Giống như mọi khả năng của gia tộc Fisalia, nó phải trả giá. Sử dụng quá lâu có thể khiến người dùng bị mắc kẹt trong chính giấc mơ của mình, làm mờ ranh giới giữa thực tại và ảo giác mãi mãi.</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Một Sinh Vật Remnant gợi nhớ đến loài udumbara trắng. Nó có thể giao tiếp với Baizhi bằng thần giao cách cảm.</t>
+          <t>Một Sinh Vật Tàn Tích gợi nhớ đến loài udumbara trắng. Nó có thể giao tiếp với Baizhi bằng thần giao cách cảm.</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Dấu vết của Echo khi chạm vào. Nó có thể xuất hiện dưới dạng đổi màu, vôi hóa, hay thậm chí là những khối san hô mọc lên, tùy thuộc vào thứ đã bị tha hóa.</t>
+          <t>Dấu vết của Tổ Tacet khi chạm vào. Nó có thể xuất hiện dưới dạng đổi màu, vôi hóa, hay thậm chí là những khối san hô mọc lên, tùy thuộc vào thứ đã bị tha hóa.</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Môn thể thao đặc trưng của Septimont, nơi Echo chiến đấu bên cạnh Chiến Binh. Chiến thắng trên đấu trường phụ thuộc vào sự phối hợp của họ.</t>
+          <t>Môn thể thao đặc trưng của Septimont, nơi Tiếng Vọng chiến đấu bên cạnh Chiến Binh. Chiến thắng trên đấu trường phụ thuộc vào sự phối hợp của họ.</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Thành phố trung tâm Septimont—nơi có Gryphon's Fortress và sân khấu của Đại Agon.</t>
+          <t>Thành phố trung tâm Septimont—nơi có Pháo Đài Gryphon và sân khấu của Đại Agon.</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Sư Tử Glory Arsinosa. Sinh ra từ tiếng reo hò chiến trận và tiếng cười, hòa quyện vào hình dáng đá của một Tacet Discord nửa người nửa sư tử hùng dũng. Từ khi ra đời, nàng đã luôn canh giữ Thành Phố Septimont.</t>
+          <t>Sư Tử Vinh Quang Arsinosa. Sinh ra từ tiếng reo hò chiến trận và tiếng cười, hòa quyện vào hình dáng đá của một Tacet Discord nửa người nửa sư tử hùng dũng. Từ khi ra đời, nàng đã luôn canh giữ Thành Phố Septimont.</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Khi Zani ở một trong các trạng thái sau, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để vào &lt;color=Highlight&gt;Ready Stance&lt;/color&gt;.
+          <t>Khi Zani ở một trong các trạng thái sau, giữ &lt;color=Highlight&gt;Kỹ năng Cộng hưởng&lt;/color&gt; để vào &lt;color=Highlight&gt;Tư thế Sẵn sàng&lt;/color&gt;.
 - Khi không ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt; và Redundant Energy đầy.
 - Khi đang ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt;.</t>
         </is>
@@ -4370,9 +4370,9 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Wolflame&lt;/color&gt;&lt;/size&gt;
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Ngọn Lửa Sói&lt;/color&gt;&lt;/size&gt;
 Lupa có thể chứa tối đa 100 điểm Ngọn Lửa Sói.
-- Khôi phục Ngọn Lửa Sói khi Tấn Công Thường trúng mục tiêu.
+- Khôi phục Ngọn Lửa Sói khi Normal Attack trúng mục tiêu.
 - Khôi phục Ngọn Lửa Sói khi sử dụng Resonance Skill.
 - Khôi phục Ngọn Lửa Sói khi sử dụng Resonance Liberation.</t>
         </is>
@@ -4442,10 +4442,10 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Wolfaith&lt;/color&gt;&lt;/size&gt;
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Niềm Tin Sói&lt;/color&gt;&lt;/size&gt;
 Lupa có thể giữ tối đa 2 điểm Niềm Tin Sói.
 Niềm Tin Sói tồn tại trong 10 giây. Thời gian sẽ được đặt lại khi Niềm Tin Sói được khôi phục. Khi hết thời gian, mỗi điểm Niềm Tin Sói còn lại sẽ chuyển thành 50 điểm Lửa Sói.
-Nhận 1 điểm Niềm Tin Sói khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Wolf's Gnawing&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Wolf's Claw&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Mid-air Attack - Firestrike&lt;/color&gt;.</t>
+Nhận 1 điểm Niềm Tin Sói khi sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Cắn Xé Của Sói&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Heavy Attack - Vuốt Sói&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không - Đòn Lửa Nổ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4512,9 +4512,9 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Pack Hunt&lt;/color&gt;&lt;/size&gt;
-Resonators sở hữu &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; được tăng 6% Tấn Công và 10% Fusion DMG khi tấn công mục tiêu thuộc hạng Overlord hoặc Calamity (không cộng dồn). Nếu đội có 3 Resonators Fusion, Fusion DMG đối với mục tiêu hạng Overlord hoặc Calamity sẽ được tăng thêm 10%. Khi Resonators hiện tại sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;, &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; sẽ được tăng cường, cộng thêm 6% Tấn Công cho tất cả Resonators trong đội, tối đa 18%.
-Nếu &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; của Lupa đạt đến giới hạn trong thời gian hiệu lực, cô sẽ bước vào trạng thái &lt;color=Highlight&gt;Wild Hunt&lt;/color&gt; và Intro Skill - &lt;color=Highlight&gt;Nowhere to Run!&lt;/color&gt; sẽ khả dụng. &lt;color=Highlight&gt;Wild Hunt&lt;/color&gt; chỉ có thể kích hoạt một lần trong thời gian &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; hiệu lực.</t>
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Săn Đoàn&lt;/color&gt;&lt;/size&gt;
+Resonator sở hữu &lt;color=Highlight&gt;Săn Đoàn&lt;/color&gt; được tăng 6% ATK và 10% Sát Thương Fusion khi tấn công mục tiêu thuộc hạng Overlord hoặc Calamity (không cộng dồn). Nếu đội có 3 Resonator Fusion, Sát Thương Fusion đối với mục tiêu hạng Overlord hoặc Calamity sẽ được tăng thêm 10%. Khi Resonator hiện tại sử dụng &lt;color=Highlight&gt;Kỹ Năng Intro&lt;/color&gt;, &lt;color=Highlight&gt;Săn Đoàn&lt;/color&gt; sẽ được tăng cường, cộng thêm 6% ATK cho tất cả Resonator trong đội, tối đa 18%.
+Nếu &lt;color=Highlight&gt;Săn Đoàn&lt;/color&gt; của Lupa đạt đến giới hạn trong thời gian hiệu lực, cô sẽ bước vào trạng thái &lt;color=Highlight&gt;Săn Hoang Dã&lt;/color&gt; và Kỹ Năng Intro - &lt;color=Highlight&gt;Không Nơi Trốn Chạy!&lt;/color&gt; sẽ khả dụng. &lt;color=Highlight&gt;Săn Hoang Dã&lt;/color&gt; chỉ có thể kích hoạt một lần trong thời gian &lt;color=Highlight&gt;Săn Đoàn&lt;/color&gt; hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Tấn Công Thường tăng tốc độ hồi phục Ngọn Lửa Sói lên 500% khi trúng mục tiêu. Không thể sử dụng Resonance Skill &lt;color=Highlight&gt;Shewolf's Hunt&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Feral Fang&lt;/color&gt; trong trạng thái này.</t>
+          <t>Normal Attack tăng tốc độ hồi phục Ngọn Lửa Sói lên 500% khi trúng mục tiêu. Không thể sử dụng Resonance Skill &lt;color=Highlight&gt;Săn Mồi Của Sói Cái&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Nanh Sói Hoang Dã&lt;/color&gt; trong trạng thái này.</t>
         </is>
       </c>
     </row>
@@ -4646,9 +4646,9 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Glory&lt;/color&gt;&lt;/size&gt;
-Kích hoạt Resonance Liberation &lt;color=Highlight&gt;Fire-Kissed Glory&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Glory&lt;/color&gt;. Trong vòng 35 giây:
-Các đòn tấn công của tất cả Resonators trong đội sẽ bỏ qua 3% Fusion RES. Với mỗi Resonators hệ Fusion khác trong đội ngoài Lupa, hiệu ứng này tăng thêm 3%, tối đa 9%. Khi đội có 3 Resonators hệ Fusion, các đòn tấn công của Resonators sẽ bỏ qua thêm 6% Fusion RES.</t>
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Vinh Quang&lt;/color&gt;&lt;/size&gt;
+Kích hoạt Resonance Liberation &lt;color=Highlight&gt;Vinh Quang Chạm Lửa&lt;/color&gt; sẽ nhận &lt;color=Highlight&gt;Vinh Quang&lt;/color&gt;. Trong vòng 35 giây:
+Các đòn tấn công của tất cả Resonator trong đội sẽ bỏ qua 3% Kháng Fusion. Với mỗi Resonator hệ Fusion khác trong đội ngoài Lupa, hiệu ứng này tăng thêm 3%, tối đa 9%. Khi đội có 3 Resonator hệ Fusion, các đòn tấn công của Resonator sẽ bỏ qua thêm 6% Kháng Fusion.</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Conviction&lt;/color&gt; đạt 120 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để sử dụng &lt;color=Highlight&gt;Resonance Liberation - Blade of Howling Squall&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Lòng Quyết Tâm&lt;/color&gt; đạt 120 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để sử dụng &lt;color=Highlight&gt;Resonance Liberation - Lưỡi Kiếm Gió Hú&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Includes Spectro Frazzle, Havoc Bane, Fusion Burst, Glacio Chafe, Electro Flare và Aero Erosion.</t>
+          <t>Bao gồm Spectro Frazzle, Havoc Bane, Fusion Burst, Glacio Chafe, Electro Flare và Aero Erosion.</t>
         </is>
       </c>
     </row>
@@ -4846,9 +4846,9 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang trong trạng thái &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt; với &lt;color=Highlight&gt;Manifest&lt;/color&gt;:
-- &lt;color=Highlight&gt;Basic Attack - Fleurdelys Stage 4&lt;/color&gt; sẽ tạo ra một trường lực để Kìm Hãm mục tiêu trong phạm vi.
-- &lt;color=Highlight&gt;Fleurdelys's&lt;/color&gt; tăng khả năng kháng gián đoạn.
+          <t>Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang trong trạng thái &lt;color=Highlight&gt;Manifest&lt;/color&gt; với &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;:
+- &lt;color=Highlight&gt;Đòn Cơ Bản - Giai Đoạn 4 của Fleurdelys&lt;/color&gt; sẽ tạo ra một trường lực để Kìm Hãm mục tiêu trong phạm vi.
+- &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; tăng khả năng kháng gián đoạn.
 - &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt; sẽ bị loại bỏ khi &lt;color=Highlight&gt;Manifest&lt;/color&gt; kết thúc.</t>
         </is>
       </c>
@@ -4916,8 +4916,8 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang trong trạng thái &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; với &lt;color=Highlight&gt;Manifest&lt;/color&gt;:
-&lt;color=Wind&gt;Aero Erosion&lt;/color&gt; sẽ được Khuếch Đại 50% sát thương và giảm 50% khoảng thời gian gây sát thương đối với kẻ địch trong một khoảng cách nhất định từ &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;.
+          <t>Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang trong trạng thái &lt;color=Highlight&gt;Manifest&lt;/color&gt; với &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt;:
+&lt;color=Wind&gt;Sói mòn Aero&lt;/color&gt; sẽ được Khuếch Đại 50% DMG và giảm 50% khoảng thời gian gây DMG đối với kẻ địch trong một khoảng cách nhất định từ &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;.
 &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; sẽ bị loại bỏ khi &lt;color=Highlight&gt;Manifest&lt;/color&gt; kết thúc.</t>
         </is>
       </c>
@@ -4985,8 +4985,8 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang trong trạng thái &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; với &lt;color=Highlight&gt;Manifest&lt;/color&gt;, sẽ nhận được hiệu ứng sau:
-Khi sử dụng &lt;color=Highlight&gt;Basic Attack - Fleurdelys Stage 5&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack - Fleurdelys Stage 2&lt;/color&gt;, &lt;color=Highlight&gt;Enhanced Heavy Attack - Fleurdelys&lt;/color&gt;, hoặc sau khi &lt;color=Highlight&gt;Resonance Skill - May Tempest Break the Tides&lt;/color&gt; gây sát thương, sẽ nâng số lượng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; trên tất cả mục tiêu lân cận lên mức cao nhất trong số các mục tiêu.
+          <t>Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang trong trạng thái &lt;color=Highlight&gt;Manifest&lt;/color&gt; với &lt;color=Highlight&gt;Power of Discord&lt;/color&gt;, sẽ nhận được hiệu ứng sau:
+Khi sử dụng &lt;color=Highlight&gt;Đòn Cơ Bản - Giai Đoạn 5 của Fleurdelys&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Trên Không - Giai Đoạn 2 của Fleurdelys&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Nặng Tăng Cường - Fleurdelys&lt;/color&gt;, hoặc sau khi &lt;color=Highlight&gt;Resonance Skill - May Tempest Break the Tides&lt;/color&gt; gây sát thương, sẽ nâng số lượng &lt;color=Wind&gt;Sói mòn Aero&lt;/color&gt; trên tất cả mục tiêu lân cận lên mức cao nhất trong số các mục tiêu.
 &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; sẽ bị loại bỏ khi &lt;color=Highlight&gt;Manifest&lt;/color&gt; kết thúc.</t>
         </is>
       </c>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Mid-air Attack - Cartethyia&lt;/color&gt;, tất cả &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; sẽ được thu hồi và dựa trên số lượng cùng loại &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; đã thu hồi, thực hiện các hình thức Đòn Lao Xuống đặc thù và nhận được &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; và &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; tương ứng.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không - Cartethyia&lt;/color&gt;, tất cả &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; sẽ được thu hồi và dựa trên số lượng cùng loại &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; đã thu hồi, thực hiện các hình thức Đòn Lao Xuống đặc thù và nhận được &lt;color=Highlight&gt;Trái Tim Đức Hạnh&lt;/color&gt;, &lt;color=Highlight&gt;Thiên Mệnh Uy Quyền&lt;/color&gt; và &lt;color=Highlight&gt;Sức Mạnh Bất Hòa&lt;/color&gt; tương ứng.</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Mid-air Attack - Cartethyia&lt;/color&gt;, tất cả &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; sẽ được thu hồi và dựa trên số lượng cùng loại &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; đã thu hồi, thực hiện các hình thức Đòn Lao Xuống đặc thù và nhận được &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; và &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; tương ứng.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không - Cartethyia&lt;/color&gt;, tất cả &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; sẽ được thu hồi và dựa trên số lượng cùng loại &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; đã thu hồi, thực hiện các hình thức Đòn Lao Xuống đặc thù và nhận được &lt;color=Highlight&gt;Trái Tim Đức Hạnh&lt;/color&gt;, &lt;color=Highlight&gt;Thiên Mệnh Uy Quyền&lt;/color&gt; và &lt;color=Highlight&gt;Sức Mạnh Bất Hòa&lt;/color&gt; tương ứng.</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Mid-air Attack - Cartethyia&lt;/color&gt;, tất cả &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; sẽ được thu hồi và dựa trên số lượng cùng loại &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; đã thu hồi, thực hiện các hình thức Đòn Lao Xuống đặc thù và nhận được &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; và &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; tương ứng.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không - Cartethyia&lt;/color&gt;, tất cả &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; sẽ được thu hồi và dựa trên số lượng cùng loại &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; đã thu hồi, thực hiện các hình thức Đòn Lao Xuống đặc thù và nhận được &lt;color=Highlight&gt;Trái Tim Đức Hạnh&lt;/color&gt;, &lt;color=Highlight&gt;Thiên Mệnh Uy Quyền&lt;/color&gt; và &lt;color=Highlight&gt;Sức Mạnh Bất Hòa&lt;/color&gt; tương ứng.</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Tiến Hóa làm khả năng cốt lõi. Một số Resonator sẽ kích hoạt Tiến Hóa một lần và nhận được hiệu ứng tăng cường sau khi ở lại chiến trường đủ số ngày nhất định.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Tiến Hóa làm khả năng cốt lõi. Một số Cộng Hưởng Giả sẽ kích hoạt Tiến Hóa một lần và nhận được hiệu ứng tăng cường sau khi ở lại chiến trường đủ số ngày nhất định.</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Nuốt Chửng làm khả năng cốt lõi. Một số Resonator sẽ trở nên mạnh mẽ hơn trong Thế Giới Giấc Mơ bằng cách Nuốt Chửng. Khi một Resonator mạnh hấp thụ kẻ khác, sản lượng Daily Coupon của nó sẽ tăng lên.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Nuốt Chửng làm khả năng cốt lõi. Một số Cộng Hưởng Giả sẽ trở nên mạnh mẽ hơn trong Thế Giới Giấc Mơ bằng cách Nuốt Chửng. Khi một Cộng Hưởng Giả mạnh hấp thụ kẻ khác, sản lượng Phiếu Hằng Ngày của nó sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Các Echoes thuộc thuộc tính Giấc Mộng này lấy Trao đổi làm khả năng cốt lõi. Trong Giấc Mộng Trao đổi, một số Echoes có thể tự Trao đổi bản thân để tái tạo Echo. Sau khi tồn tại trong Giấc Mộng đủ số ngày quy định, chúng sẽ Tự Loại Bỏ và để lại nhiều hiệu ứng tăng cường.</t>
+          <t>Các Echo thuộc thuộc tính Giấc Mộng này lấy Trao Đổi làm khả năng cốt lõi. Trong Giấc Mộng Trao Đổi, một số Echo có thể tự Trao Đổi bản thân để tái tạo Tổ Tacet. Sau khi tồn tại trong Giấc Mộng đủ số ngày quy định, chúng sẽ Tự Loại Bỏ và để lại nhiều hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này có thể gây ra những biến đổi đáng kể trong giấc mơ thông qua Sự Kết Hợp. Khi đạt đủ điều kiện, một số Resonator sẽ hòa nhập với Resonator khác cùng hàng để tạo thành một Resonator hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường khác nhau.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này có thể gây ra những biến đổi đáng kể trong giấc mơ thông qua Sự Kết Hợp. Khi đạt đủ điều kiện, một số Cộng Hưởng Giả sẽ hòa nhập với Cộng Hưởng Giả khác cùng hàng để tạo thành một Cộng Hưởng Giả hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Các Echoes thuộc thuộc tính Giấc Mộng này không có khả năng đặc biệt và rất phù hợp để kết hợp với các Echoes thuộc thuộc tính Giấc Mộng khác. Những Echoes này sẽ tự động được thêm vào Tuyển Dụng Echoes sau khi mở khóa.</t>
+          <t>Các Echo thuộc thuộc tính Giấc Mộng này không có khả năng đặc biệt và rất phù hợp để kết hợp với các Echo thuộc thuộc tính Giấc Mộng khác. Những Echo này sẽ tự động được thêm vào Tuyển Dụng Echo sau khi mở khóa.</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này có thể trở nên mạnh mẽ hơn thông qua Sự Tiến Hóa. Khi đạt đủ điều kiện Tiến Hóa, sản lượng Daily Coupon của chúng sẽ tăng lên.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này có thể trở nên mạnh mẽ hơn thông qua Sự Tiến Hóa. Khi đạt đủ điều kiện Tiến Hóa, sản lượng Phiếu Hằng Ngày của chúng sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Nuốt Chửng làm khả năng cốt lõi. Một số Resonator sẽ trở nên mạnh mẽ hơn trong Thế Giới Giấc Mơ bằng cách Nuốt Chửng. Khi một Resonator mạnh hấp thụ kẻ yếu hơn, sản lượng Daily Coupon của nó sẽ tăng lên.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Nuốt Chửng làm khả năng cốt lõi. Một số Cộng Hưởng Giả sẽ trở nên mạnh mẽ hơn trong Thế Giới Giấc Mơ bằng cách Nuốt Chửng. Khi một Cộng Hưởng Giả mạnh hấp thụ kẻ yếu hơn, sản lượng Phiếu Hằng Ngày của nó sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Các Echoes thuộc thuộc tính Giấc Mộng này lấy Trao đổi làm khả năng cốt lõi. Một số Echoes có thể tự Trao đổi bản thân để tái tạo Echo. Sau khi tồn tại trong Giấc Mộng đủ số ngày quy định, chúng sẽ Tự Loại Bỏ và để lại nhiều hiệu ứng tăng cường.</t>
+          <t>Các Echo thuộc thuộc tính Giấc Mộng này lấy Trao Đổi làm khả năng cốt lõi. Một số Echo có thể tự Trao Đổi bản thân để tái tạo Tổ Tacet. Sau khi tồn tại trong Giấc Mộng đủ số ngày quy định, chúng sẽ Tự Loại Bỏ và để lại nhiều hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Các Echoes thuộc thuộc tính Giấc Mộng này lấy Integration làm khả năng cốt lõi. Một số Echoes có thể tái tạo Echo thông qua Integration. Khi điều kiện được đáp ứng, các Echoes liền kề sẽ hòa làm một thành Echoes hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường.</t>
+          <t>Các Echo thuộc thuộc tính Giấc Mộng này lấy Hợp Nhất làm khả năng cốt lõi. Một số Echo có thể tái tạo Tổ Tacet thông qua Hợp Nhất. Khi điều kiện được đáp ứng, các Echo liền kề sẽ hòa làm một thành Echo hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Sản lượng phiếu thưởng hàng ngày là số lượng Dreamland Coupons cơ bản mà các Resonator có thể thu thập mỗi ngày.</t>
+          <t>Sản lượng phiếu thưởng hàng ngày là số lượng Phiếu Dreamland cơ bản mà các Cộng Hưởng Giả có thể thu thập mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Những phiếu giảm giá mà Echoes thu thập để đạt chỉ tiêu doanh thu và giữ cho Dreamland ổn định.</t>
+          <t>Những phiếu giảm giá mà Echo thu thập để đạt chỉ tiêu doanh thu và giữ cho Dreamland ổn định.</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Số Echoes nhận được từ Daily Coupon trên các Dream Block này tăng thêm 2.</t>
+          <t>Số Echo nhận được từ Phiếu Hằng Ngày trên các Khối Mộng này tăng thêm 2.</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Tất cả Echoes trên các Dream Block này được coi là cùng một hàng.</t>
+          <t>Tất cả Echo trên các Khối Mộng Ảo này được coi là cùng một hàng.</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Một cuộn giấy Lillibet mang theo, ghi lại những khải tượng cô nhìn thấy trong ánh lửa. Cả cuốn sách này lẫn những bức bích họa trong Tetragon Temple đều là phương tiện mà các Nữ Tư Tế Septimont dùng để truyền đạt lời tiên tri cho dân chúng.</t>
+          <t>Một cuộn giấy Lillibet mang theo, ghi lại những khải tượng cô nhìn thấy trong ánh lửa. Cả cuốn sách này lẫn những bức bích họa trong Đền Tetragon đều là phương tiện mà các Nữ Tư Tế Septimont dùng để truyền đạt lời tiên tri cho dân chúng.</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro của Phrolova, được tạo ra để tái hiện Thế Giới Bên Kia bằng phương pháp nhân tạo. Dùng sức mạnh của Threnodian Leviathan, cô dự định sử dụng thân thể của các Tacet Discord làm vật chủ cho ý thức vang vọng của những người đã khuất. Như vậy, Sonoro có thể hòa nhập với thực tại, và những linh hồn đã mất sẽ được sống trong một thế giới vĩnh hằng mới, không còn sự hủy hoại.</t>
+          <t>Sonoro Sphere của Phrolova, được tạo ra để tái hiện Thế Giới Bên Kia bằng phương pháp nhân tạo. Dùng sức mạnh của Threnodian Leviathan, cô dự định sử dụng thân thể của các Tacet Discord làm vật chủ cho ý thức vang vọng của những người đã khuất. Như vậy, Sonoro có thể hòa nhập với thực tại, và những linh hồn đã mất sẽ được sống trong một thế giới vĩnh hằng mới, không còn sự hủy hoại.</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Thiết bị ấp trứng Echoes Common. Các tần số Echoes bị xoắn vặn, vỡ vụn được tái cấu trúc thành Echoes Common mới trong buồng ấp.</t>
+          <t>Thiết bị ấp trứng Echo Thường. Các tần số Echo bị xoắn vặn, vỡ vụn được tái cấu trúc thành Echo Thường mới trong buồng ấp.</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Một hiện tượng Waveworn độc nhất ở Rinascita, Sóng Đen là biểu hiện sức mạnh Thống Nhất của Threnodian Leviathan. Mây đen dày đặc tụ lại trên cao rồi đổ sập xuống như thác nước, tràn ra khắp nơi. Nơi nào Sóng Đen lan tới, Tacet Discord sẽ xuất hiện và đất đai bị nhiễm Tidal Blight. Tại tâm điểm, một Tacet Field mới hình thành.</t>
+          <t>Một hiện tượng Waveworn độc nhất ở Rinascita, Sóng Đen là biểu hiện sức mạnh Thống Nhất của Threnodian Leviathan. Mây đen dày đặc tụ lại trên cao rồi đổ sập xuống như thác nước, tràn ra khắp nơi. Nơi nào Sóng Đen lan tới, Tacet Discord sẽ xuất hiện và đất đai bị nhiễm Tidal Blight. Tại tâm điểm, một Tổ Tacet mới hình thành.</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Năng lượng Tàn Dư Siêu Đậm Đặc từ Etheric Sea, tái hiện quá khứ với độ chân thực kỳ lạ. Retroact Rain trải qua ba giai đoạn: rơi tự nhiên, lơ lửng gần mặt đất, và dòng chảy ngược.</t>
+          <t>Năng lượng Tàn Dư Siêu Đậm Đặc từ Biển Ether, tái hiện quá khứ với độ chân thực kỳ lạ. Mưa Retroact trải qua ba giai đoạn: rơi tự nhiên, lơ lửng gần mặt đất, và dòng chảy ngược.</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Sanguis Plateaus từng là tiền tuyến của Septimont chống lại Dark Tide. Do địa hình đặc biệt của vùng đất này, năng lượng Remnant tích tụ ở đây với mật độ dày đặc, cùng với đám mây Blightcloud vĩnh viễn treo lơ lửng trên đầu, hình thành từ đợt Dark Tide đầu tiên. Vào mùa High Tide, các Gladiator từ khắp Septimont đổ về đây săn lùng những sinh vật Dark Tide để giành lấy vinh quang.</t>
+          <t>Cao Nguyên Sanguis từng là tiền tuyến của Septimont chống lại Dark Tide. Do địa hình đặc biệt của vùng đất này, năng lượng Remnant tích tụ ở đây với mật độ dày đặc, cùng với đám mây Blightcloud vĩnh viễn treo lơ lửng trên đầu, hình thành từ đợt Dark Tide đầu tiên. Vào mùa High Tide, các Gladiator từ khắp Septimont đổ về đây săn lùng những sinh vật Dark Tide để giành lấy vinh quang.</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Khi một Echo on the field bị Nuốt Chửng, có 20% khả năng tạo ra Hình Thái Cơ Bản của nó trên một ô trống.</t>
+          <t>Khi một Tổ Tacet trên chiến trường bị Nuốt Chửng, có 20% khả năng tạo ra Hình Thái Cơ Bản của nó trên một ô trống.</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Khi một Echo trải qua Tiến Hóa, có 5% khả năng tăng lượng Daily Coupon tạo ra lên 100%.</t>
+          <t>Khi một Tổ Tacet trải qua Tiến Hóa, có 5% khả năng tăng lượng Phiếu Hằng Ngày tạo ra lên 100%.</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Mỗi khi thu thập được 10 Echoes (không tính từ Echoes Recruitment, Shop hoặc Phantasma Blessing), nhận 2 Tinh Thể Tần Số.</t>
+          <t>Mỗi khi thu thập được 10 Echo (không tính từ Echo Recruitment, Shop hoặc Phantasma Blessing), nhận 2 Tinh Thể Tần Số.</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Mỗi Echo hạng xanh trên chiến trường, khi Trao đổi một Vật Phẩm Giao Dịch, có 5% cơ hội tạo ra một Echo cùng tên, có thể chồng chất tối đa 5 lần.</t>
+          <t>Mỗi Echo hạng xanh trên chiến trường, khi Trao Đổi một Vật Phẩm Giao Dịch, có 5% cơ hội tạo ra một Echo cùng tên, có thể chồng chất tối đa 5 lần.</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Echo đầu tiên kích hoạt Integration sẽ cần ít hơn 1 Echo.</t>
+          <t>Echo đầu tiên kích hoạt Hợp Nhất sẽ cần ít hơn 1 Echo.</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Dreamland Coupons nhận từ nguồn khác ngoài Echoe Daily Coupon sẽ được tăng thêm 10%.</t>
+          <t>Phiếu Giấc Mơ nhận từ nguồn khác ngoài Echoe Daily Coupon sẽ được tăng thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Nhận 5 Dreamland Coupons mỗi khi xảy ra Hiện Tượng Nuốt Chửng.</t>
+          <t>Nhận 5 Phiếu Giấc Mơ mỗi khi xảy ra Hiện Tượng Nuốt Chửng.</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Khi một Echo Tự Hủy hoặc được Hấp Thu vào một new Echo, bạn sẽ nhận thêm Dreamland Coupons bằng với lượng Daily Coupon mà nó tạo ra.</t>
+          <t>Khi một Tổ Tacet Tự Hủy hoặc được Hấp Thu vào một Tổ Tacet mới, bạn sẽ nhận thêm Phiếu Mộng Ảo bằng với lượng Phiếu Hằng Ngày mà nó tạo ra.</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Mỗi khi thu thập được 10 Echoes (không tính từ Echoes Recruitment, Shop hoặc Phantasma Blessing), nhận thêm 500 Dreamland Couponss.</t>
+          <t>Mỗi khi thu thập được 10 Echo (không tính từ Echo Recruitment, Shop hoặc Phantasma Blessing), nhận thêm 500 Dreamland Coupons.</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nhận Dreamland Coupons tương đương số lượng Tinh thể Tần số trong mỗi Giai đoạn.</t>
+          <t>Nhận Dreamland Coupon tương đương số lượng Tinh thể Tần số trong mỗi Giai đoạn.</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Echoes được coi là Đã Loại Bỏ khi bị Trao Đổi, Hấp Thu, Nuốt Chửng hoặc Tự Loại Bỏ. Giải tán Echoes không được tính là Loại Bỏ.</t>
+          <t>Echo được coi là Đã Loại Bỏ khi bị Trao Đổi, Hấp Thu, Nuốt Chửng hoặc Tự Loại Bỏ. Giải tán Echo không được tính là Loại Bỏ.</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Integration: Khi 3 Echoes cùng Thuộc Tính Giấc Mơ và độ hiếm với Echoes này đứng cùng hàng, chúng sẽ Integration thành 1 Rage Against the Statue và nhận được Dreamland Coupons tương đương 60 + tổng số Daily Coupon x2.</t>
+          <t>Hợp Nhất: Khi 3 Echo cùng Thuộc Tính Giấc Mơ và độ hiếm với Echo này đứng cùng hàng, chúng sẽ Hợp Nhất thành 1 Rage Against the Statue và nhận được Dreamland Coupon tương đương 60 + tổng số Coupon Hằng Ngày x2.</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Integration: Khi 3 Echoes cùng Thuộc Tính Giấc Mơ và độ hiếm với Echoes này đứng cùng hàng, chúng sẽ Integration thành 1 Crownless và nhận được Dreamland Coupons tương đương 150 + tổng số Daily Coupon x3.</t>
+          <t>Hợp Nhất: Khi 3 Echo cùng Thuộc Tính Giấc Mơ và độ hiếm với Echo này đứng cùng hàng, chúng sẽ Hợp Nhất thành 1 Crownless và nhận được Dreamland Coupon tương đương 150 + tổng số Coupon Hằng Ngày x3.</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Integration: Khi 3 Echoes cùng Thuộc Tính Giấc Mơ và độ hiếm với Echoes này đứng cùng hàng, chúng sẽ Integration thành 1 Crownless và nhận được Dreamland Coupons tương đương 450 + tổng số Daily Coupon x4. Số Daily Coupon của nó bằng tổng số Daily Coupon của tất cả các Echoes đã Integration.</t>
+          <t>Hợp Nhất: Khi 3 Echo cùng Thuộc Tính Giấc Mơ và độ hiếm với Echo này đứng cùng hàng, chúng sẽ Hợp Nhất thành 1 Crownless và nhận được Dreamland Coupon tương đương 450 + tổng số Coupon Hằng Ngày x4. Số Coupon Hằng Ngày của nó bằng tổng số Coupon Hằng Ngày của tất cả các Echo đã Hợp Nhất.</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Integration: Khi 3 Echoes cùng Thuộc Tính Giấc Mơ và độ hiếm với Echoes này đứng cùng hàng, chúng sẽ Integration thành 1 Stonewall Bracer và nhận được Dreamland Coupons tương đương 30 + tổng số Daily Coupon x1.</t>
+          <t>Hợp Nhất: Khi 3 Echo cùng Thuộc Tính Giấc Mơ và độ hiếm với Echo này đứng cùng hàng, chúng sẽ Hợp Nhất thành 1 Stonewall Bracer và nhận được Dreamland Coupon tương đương 30 + tổng số Coupon Hằng Ngày x1.</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Trao đổi: Sau 2 ngày, sẽ tự loại bỏ bản thân khỏi Vật Phẩm Trao đổi. Dấu Vết này luôn xuất hiện trên cùng một khối. Khi Trao đổi, có 50% cơ hội tạo ra một Mourning Aix trên khối trống. Không thể nhận được Dấu Vết này qua Echo Recruitment.</t>
+          <t>Trao Đổi: Sau 2 ngày, sẽ tự loại bỏ bản thân khỏi Vật Phẩm Trao Đổi. Dấu Vết này luôn xuất hiện trên cùng một khối. Khi Trao Đổi, có 50% cơ hội tạo ra một Mourning Aix trên khối trống. Không thể nhận được Dấu Vết này qua Echo Recruitment.</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Số Echoes nhận được từ Daily Coupon trên các Dream Block này tạm thời tăng thêm 2. Phần thưởng sẽ bị hủy khi rời khỏi khu vực này.</t>
+          <t>Số Echo nhận được từ Phiếu Hằng Ngày trên các Khối Mộng này tạm thời tăng thêm 2. Phần thưởng sẽ bị hủy khi rời khỏi khu vực này.</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Các Echoes có hiệu ứng này được coi là liền kề nhau.</t>
+          <t>Các Echo có hiệu ứng này được coi là liền kề nhau.</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Các Echoes có hiệu ứng này được coi là cùng hàng.</t>
+          <t>Các Echo có hiệu ứng này được coi là cùng hàng.</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Các Echoes có hiệu ứng này có thể được coi là thuộc bất kỳ cấp hiếm nào.</t>
+          <t>Các Echo có hiệu ứng này có thể được coi là thuộc bất kỳ cấp hiếm nào.</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Gradation: Hiện tượng Gradation xảy ra mỗi 6 ngày. Sau mỗi lần Gradation, tăng tiến trình Gradation của các Echo Có Thể Gradation cùng hàng lên 1, tối đa 2 lần mỗi ngày.</t>
+          <t>Phân Cấp: Hiện tượng Phân Cấp xảy ra mỗi 6 ngày. Sau mỗi lần Phân Cấp, tăng tiến trình Phân Cấp của các Tiếng Vọng Có Thể Phân Cấp cùng hàng lên 1, tối đa 2 lần mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Echo Roseshroom bao gồm: Roseshroom Con, Roseshroom, Dreamborne: Roseshroom Con, Dreamborne: Roseshroom.</t>
+          <t>Tiếng Vọng Nấm Hồng bao gồm: Baby Roseshroom, Roseshroom, Dreamborne: Baby Roseshroom, Dreamborne: Roseshroom.</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Devour: Mỗi ngày, nuốt chửng 1 Echoes liền kề hiếm cấp xám hoặc xanh, nhận được lượng Daily Coupon mà mục tiêu bị nuốt chửng tạo ra. Ưu tiên nuốt chửng Prism Echoes.</t>
+          <t>Nuốt chửng: Mỗi ngày, nuốt chửng 1 Echo liền kề hiếm cấp xám hoặc xanh, nhận được lượng Daily Coupon mà mục tiêu bị nuốt chửng tạo ra. Ưu tiên nuốt chửng Prism Echo.</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Khi một Echo on the field bắt đầu Hấp Thu, có 20% khả năng tạo ra một bản sao của Echo đó.</t>
+          <t>Khi một Tổ Tacet trên chiến trường bắt đầu Hấp Thu, có 20% khả năng tạo ra một bản sao của Tổ Tacet đó.</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khi một đơn vị bị Loại Bỏ, tăng sản lượng Daily Coupon của chính nó lên 2, tối đa 1 lần mỗi ngày.</t>
+          <t>Khi một đơn vị bị Loại Bỏ, tăng sản lượng Phiếu Hằng Ngày của chính nó lên 2, tối đa 1 lần mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Trao đổi: Sau 2 ngày, sẽ tự loại bỏ bản thân khỏi Vật Phẩm Trao đổi. Khi Trao đổi, sản lượng Daily Coupon của các Dấu Vết liền kề tăng thêm 30% sản lượng Daily Coupon của Dấu Vết này. Không thể nhận được Dấu Vết này qua Echoes Recruitment.</t>
+          <t>Trao Đổi: Sau 2 ngày, sẽ tự loại bỏ bản thân khỏi Vật Phẩm Trao Đổi. Khi Trao Đổi, sản lượng Phiếu Hằng Ngày của các Dấu Vết liền kề tăng thêm 30% sản lượng Phiếu Hằng Ngày của Dấu Vết này. Không thể nhận được Dấu Vết này qua Echo Recruitment.</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Trao đổi: Sau 2 ngày, sẽ tự loại bỏ bản thân khỏi Vật Phẩm Trao đổi. Khi Trao đổi hoặc Bị Nuốt Chửng, sẽ nhận được Dreamland Coupons bằng sản lượng Daily Coupon hiện tại x10. Có 50% cơ hội tạo ra một Mourning Aix. Không thể nhận được Dấu Vết này qua Echo Recruitment.</t>
+          <t>Trao Đổi: Sau 2 ngày, sẽ tự loại bỏ bản thân khỏi Vật Phẩm Trao Đổi. Khi Trao Đổi hoặc Bị Nuốt Chửng, sẽ nhận được Phiếu Dreamland bằng sản lượng Phiếu Hằng Ngày hiện tại x10. Có 50% cơ hội tạo ra một Mourning Aix. Không thể nhận được Dấu Vết này qua Echo Recruitment.</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tất cả Echoes trên các Dream Block này được coi là kề nhau.</t>
+          <t>Tất cả Echo trên các Khối Mộng Ảo này được coi là kề nhau.</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Tower vô tuyến nằm ở trung tâm Honami City và là tòa nhà cao nhất thành phố. Đây từng là điểm du lịch nổi tiếng nhất và biểu tượng của Honami. Người ta nói rằng Lament đã hủy diệt thành phố này bắt đầu từ Neon Tower.</t>
+          <t>Tháp vô tuyến nằm ở trung tâm Thành phố Honami và là tòa nhà cao nhất thành phố. Đây từng là điểm du lịch nổi tiếng nhất và biểu tượng của Honami. Người ta nói rằng Lament đã hủy diệt thành phố này bắt đầu từ Tháp Neon.</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Những công dân của Honami City đã qua đời trong Lament và giờ đây "sống" bên trong Sonoro Sphere dưới hình hài Dư Âm Nhân Loại. Ánh sáng lấp lánh mờ ảo bao quanh thân thể họ, và họ dường như không hề hay biết chuyện gì đã thực sự xảy ra với mình.</t>
+          <t>Những công dân của Thành phố Honami đã qua đời trong Lament và giờ đây "sống" bên trong Sonoro Sphere dưới hình hài Dư Âm Nhân Loại. Ánh sáng lấp lánh mờ ảo bao quanh thân thể họ, và họ dường như không hề hay biết chuyện gì đã thực sự xảy ra với mình.</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ánh sáng cầu vồng nhạt màu trào dâng trong Sonoro Sphere của Honami City là một Waveworn Phenomenon độc nhất ở nơi này. Traces của sự tha hóa Irideglow có thể tìm thấy khắp Honami. Trong các đợt bùng phát Lament định kỳ, Irideglow cô đặc lại thành hình dạng vật lý, xuyên qua không gian, bắt giữ và nuốt chửng mọi thứ nó gặp trong Sonoro. Những Resonators tiếp xúc lâu dài với Irideglow có nguy cơ cao mất kiểm soát sức mạnh Resonance, thậm chí bị Overclock.</t>
+          <t>Ánh sáng cầu vồng nhạt màu trào dâng trong Sonoro Sphere của Honami City là một Waveworn Phenomenon độc nhất ở nơi này. Dấu vết của sự tha hóa Irideglow có thể tìm thấy khắp Honami. Trong các đợt bùng phát Lament định kỳ, Irideglow cô đặc lại thành hình dạng vật lý, xuyên qua không gian, bắt giữ và nuốt chửng mọi thứ nó gặp trong Sonoro. Những Resonator tiếp xúc lâu dài với Irideglow có nguy cơ cao mất kiểm soát sức mạnh Cộng Hưởng, thậm chí bị Overclock.</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Những vướng mắc, lưu luyến chưa trọn của những kẻ Bị Bỏ Lại vương vãi khắp thành phố Honami. Chúng mang một đặc tính đặc biệt, có thể cộng hưởng với Neon Tower, giúp chủ nhân xác định vị trí của tháp trong không gian chồng chéo hỗn loạn.</t>
+          <t>Những vướng mắc, lưu luyến chưa trọn của những kẻ Bị Bỏ Lại vương vãi khắp thành phố Honami. Chúng mang một đặc tính đặc biệt, có thể cộng hưởng với Tháp Neon, giúp chủ nhân xác định vị trí của tháp trong không gian chồng chéo hỗn loạn.</t>
         </is>
       </c>
     </row>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Traces kết tinh còn sót lại trên bề mặt các tòa nhà và vật thể do sự nhiễm độc Irideglow. Những tinh thể Irideglow bị nhiễm độc nhẹ—tinh thể Irideglow Light—có thể được tách ra bằng một số phương pháp nhất định.</t>
+          <t>Dấu vết kết tinh còn sót lại trên bề mặt các tòa nhà và vật thể do sự nhiễm độc Irideglow. Những tinh thể Irideglow bị nhiễm độc nhẹ—tinh thể Irideglow Ánh Sáng—có thể được tách ra bằng một số phương pháp nhất định.</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Startorch Academy là một cơ sở nghiên cứu tổng hợp không thuộc bất kỳ quốc gia nào, được xây dựng với mục tiêu hợp tác nghiên cứu khoa học. Đây là một đô thị học thuật vận hành hoàn toàn vì giáo dục và nghiên cứu. So với cái tên chính thức "Startorch Academy", người dân Solaris thích gọi nơi này là "Học viện Resonator" hơn.</t>
+          <t>Học viện Startorch là một cơ sở nghiên cứu tổng hợp không thuộc bất kỳ quốc gia nào, được xây dựng với mục tiêu hợp tác nghiên cứu khoa học. Đây là một đô thị học thuật vận hành hoàn toàn vì giáo dục và nghiên cứu. So với cái tên chính thức "Học viện Startorch", người dân Solaris thích gọi nơi này là "Học viện Resonator" hơn.</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Một tổ chức khoa học quốc tế được thành lập bởi nhiều quốc gia và tổ chức trên Solaris. Tổ chức này giám sát nghiên cứu, phát triển và xây dựng tại Lahai-Roi. Chính Spacetrek Collective đã xây dựng Viện Nghiên Cứu và Startorch Academy trong không gian rộng lớn bên dưới vùng băng giá.</t>
+          <t>Một tổ chức khoa học quốc tế được thành lập bởi nhiều quốc gia và tổ chức trên Solaris. Tổ chức này giám sát nghiên cứu, phát triển và xây dựng tại Lahai-Roi. Chính Spacetrek Collective đã xây dựng Viện Nghiên cứu và Học viện Startorch trong không gian rộng lớn bên dưới vùng băng giá.</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Sinh vật Remnant này sống bên trong Quả Cầu Sonoro của Honami City được cho là linh vật của thành phố trước khi nơi đây bị hủy diệt. "Namipon" ban đầu được tạo ra như một linh vật giao thông đô thị, bảo vệ những chuyến đi hàng ngày của người dân, di chuyển với tốc độ siêu thanh giữa các tuyến đường sắt trong thành phố. Về sau, nó dần phát triển thành linh vật đại diện cho nhiều mặt của thành phố.</t>
+          <t>Sinh vật Tàn Tích này sống bên trong Sonoro Sphere của Thành phố Honami được cho là linh vật của thành phố trước khi nơi đây bị hủy diệt. "Namipon" ban đầu được tạo ra như một linh vật giao thông đô thị, bảo vệ những chuyến đi hàng ngày của người dân, di chuyển với tốc độ siêu thanh giữa các tuyến đường sắt trong thành phố. Về sau, nó dần phát triển thành linh vật đại diện cho nhiều mặt của thành phố.</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Quốc gia bao trùm Honami City. Dù thường xuyên hứng chịu Hiện tượng Waveworn, nơi đây vẫn duy trì một xã hội thịnh vượng và đô thị hóa cao độ, nổi bật với mạng lưới đường sắt trải dài.</t>
+          <t>Quốc gia bao trùm Thành phố Honami. Dù thường xuyên hứng chịu Hiện tượng Waveworn, nơi đây vẫn duy trì một xã hội thịnh vượng và đô thị hóa cao độ, nổi bật với mạng lưới đường sắt trải dài.</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       <c r="M149" t="inlineStr">
         <is>
           <t>Một "mỏ neo" còn sót lại khi Exostrider lần đầu đặt chân đến vùng đất sau này được gọi là Lahai-Roi.
-Spacetrek Collective đã nhiều lần tổ chức thám hiểm đến địa điểm này, nhưng chẳng thu được gì đáng ghi chép.</t>
+Tập Đoàn Spacetrek đã nhiều lần tổ chức thám hiểm đến địa điểm này, nhưng chẳng thu được gì đáng ghi chép.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       <c r="M150" t="inlineStr">
         <is>
           <t>Điểm vào hình thành khi Exostrider và Threnodian Aleph-1 xâm nhập Solaris. Mạng lưới rễ Soliskin bên trên đang kìm hãm sức mạnh của Aleph-1, những "cánh cửa bị phong ấn" của Stridergate.
-Khối Keystone chính là "ổ khóa" giữ cho Stridergate đóng chặt.
+Khối Đá Chìa Khóa chính là "ổ khóa" giữ cho Stridergate đóng chặt.
 Phía sau đó có lẽ là "vũ trụ" mà Solaris luôn khao khát khám phá.</t>
         </is>
       </c>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Cooldown Resonance Skill Giảm Một Nửa</t>
+          <t>Thời gian hồi Resonance Skill Giảm Một Nửa</t>
         </is>
       </c>
     </row>
